--- a/batch_bot_manual/data/sample_data.xlsx
+++ b/batch_bot_manual/data/sample_data.xlsx
@@ -582,7 +582,8 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Failed: Message: invalid session id; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdr</t>
+          <t>Failed: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="input_1"]"}
+  (Session inf</t>
         </is>
       </c>
     </row>
@@ -913,7 +914,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
